--- a/data/trans_camb/P2A_enfcro_R-Estudios-trans_camb.xlsx
+++ b/data/trans_camb/P2A_enfcro_R-Estudios-trans_camb.xlsx
@@ -677,47 +677,47 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
-          <t>-11,66; 18,62</t>
+          <t>-10,12; 19,46</t>
         </is>
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>-18,77; 14,58</t>
+          <t>-17,65; 16,49</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>21,03; 45,98</t>
+          <t>21,91; 46,31</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>-15,73; 13,9</t>
+          <t>-15,77; 13,71</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
         <is>
-          <t>-30,56; 1,74</t>
+          <t>-29,93; 1,25</t>
         </is>
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>13,79; 39,57</t>
+          <t>13,47; 38,28</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>-9,44; 12,04</t>
+          <t>-10,6; 11,2</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
         <is>
-          <t>-19,25; 2,3</t>
+          <t>-20,07; 2,78</t>
         </is>
       </c>
       <c r="K5" s="2" t="inlineStr">
         <is>
-          <t>20,04; 38,15</t>
+          <t>20,74; 38,45</t>
         </is>
       </c>
     </row>
@@ -783,47 +783,47 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
-          <t>-18,55; 37,43</t>
+          <t>-15,76; 39,44</t>
         </is>
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>-29,05; 29,59</t>
+          <t>-27,82; 32,62</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>31,78; 96,76</t>
+          <t>33,17; 98,59</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>-23,17; 25,21</t>
+          <t>-22,41; 25,37</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
         <is>
-          <t>-43,77; 3,38</t>
+          <t>-42,74; 2,4</t>
         </is>
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>18,86; 75,84</t>
+          <t>18,22; 71,87</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>-14,4; 21,96</t>
+          <t>-16,08; 20,13</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
         <is>
-          <t>-29,77; 4,09</t>
+          <t>-31,01; 4,79</t>
         </is>
       </c>
       <c r="K7" s="2" t="inlineStr">
         <is>
-          <t>29,37; 72,24</t>
+          <t>30,69; 72,12</t>
         </is>
       </c>
     </row>
@@ -893,47 +893,47 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>-0,04; 13,27</t>
+          <t>0,22; 13,55</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>-3,21; 8,93</t>
+          <t>-2,96; 9,09</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>50,24; 60,19</t>
+          <t>50,54; 60,13</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>-0,51; 12,11</t>
+          <t>0,2; 12,53</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>-6,46; 5,83</t>
+          <t>-6,49; 4,94</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>47,91; 57,1</t>
+          <t>46,68; 56,53</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>2,29; 10,94</t>
+          <t>2,19; 11,37</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
         <is>
-          <t>-3,38; 5,15</t>
+          <t>-3,54; 4,93</t>
         </is>
       </c>
       <c r="K9" s="2" t="inlineStr">
         <is>
-          <t>50,31; 56,98</t>
+          <t>50,19; 57,37</t>
         </is>
       </c>
     </row>
@@ -999,47 +999,47 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
-          <t>-0,14; 36,88</t>
+          <t>0,63; 38,37</t>
         </is>
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>-7,6; 25,13</t>
+          <t>-6,96; 25,08</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>116,1; 174,19</t>
+          <t>118,21; 175,81</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>-1,19; 30,24</t>
+          <t>0,42; 32,48</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
         <is>
-          <t>-14,29; 15,38</t>
+          <t>-14,48; 12,78</t>
         </is>
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>104,46; 151,42</t>
+          <t>99,65; 147,68</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>5,41; 28,33</t>
+          <t>4,87; 29,39</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
         <is>
-          <t>-7,97; 13,74</t>
+          <t>-8,35; 12,63</t>
         </is>
       </c>
       <c r="K11" s="2" t="inlineStr">
         <is>
-          <t>116,25; 152,54</t>
+          <t>115,32; 152,75</t>
         </is>
       </c>
     </row>
@@ -1109,47 +1109,47 @@
       </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
-          <t>-2,27; 17,45</t>
+          <t>-3,51; 17,42</t>
         </is>
       </c>
       <c r="D13" s="2" t="inlineStr">
         <is>
-          <t>-4,37; 14,34</t>
+          <t>-4,05; 15,16</t>
         </is>
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>58,19; 72,06</t>
+          <t>58,25; 71,56</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>-3,89; 15,2</t>
+          <t>-5,43; 14,69</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
         <is>
-          <t>-8,15; 10,62</t>
+          <t>-8,36; 10,95</t>
         </is>
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>54,94; 68,9</t>
+          <t>54,59; 68,93</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>-1,04; 12,82</t>
+          <t>-1,13; 13,28</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
         <is>
-          <t>-3,47; 10,36</t>
+          <t>-2,71; 10,79</t>
         </is>
       </c>
       <c r="K13" s="2" t="inlineStr">
         <is>
-          <t>58,18; 68,06</t>
+          <t>58,05; 68,4</t>
         </is>
       </c>
     </row>
@@ -1215,47 +1215,47 @@
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
-          <t>-6,28; 57,1</t>
+          <t>-8,8; 56,8</t>
         </is>
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>-11,11; 47,89</t>
+          <t>-9,72; 50,0</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>139,79; 256,22</t>
+          <t>140,29; 254,63</t>
         </is>
       </c>
       <c r="F15" s="2" t="inlineStr">
         <is>
-          <t>-9,33; 48,06</t>
+          <t>-12,75; 46,24</t>
         </is>
       </c>
       <c r="G15" s="2" t="inlineStr">
         <is>
-          <t>-19,57; 33,48</t>
+          <t>-20,78; 34,54</t>
         </is>
       </c>
       <c r="H15" s="2" t="inlineStr">
         <is>
-          <t>126,24; 229,35</t>
+          <t>124,04; 229,66</t>
         </is>
       </c>
       <c r="I15" s="2" t="inlineStr">
         <is>
-          <t>-2,85; 39,49</t>
+          <t>-2,88; 41,35</t>
         </is>
       </c>
       <c r="J15" s="2" t="inlineStr">
         <is>
-          <t>-9,04; 31,68</t>
+          <t>-6,77; 33,69</t>
         </is>
       </c>
       <c r="K15" s="2" t="inlineStr">
         <is>
-          <t>142,67; 218,21</t>
+          <t>142,16; 222,36</t>
         </is>
       </c>
     </row>
@@ -1325,47 +1325,47 @@
       </c>
       <c r="C17" s="2" t="inlineStr">
         <is>
-          <t>2,14; 12,01</t>
+          <t>1,3; 11,69</t>
         </is>
       </c>
       <c r="D17" s="2" t="inlineStr">
         <is>
-          <t>-2,49; 7,43</t>
+          <t>-2,2; 7,93</t>
         </is>
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>51,3; 58,96</t>
+          <t>51,47; 59,01</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>0,78; 10,25</t>
+          <t>-0,08; 9,98</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
         <is>
-          <t>-6,55; 3,11</t>
+          <t>-6,51; 3,05</t>
         </is>
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>47,92; 55,59</t>
+          <t>48,12; 55,69</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>2,46; 9,48</t>
+          <t>2,43; 9,85</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
         <is>
-          <t>-3,25; 3,7</t>
+          <t>-3,34; 3,85</t>
         </is>
       </c>
       <c r="K17" s="2" t="inlineStr">
         <is>
-          <t>50,93; 55,89</t>
+          <t>50,54; 56,17</t>
         </is>
       </c>
     </row>
@@ -1431,47 +1431,47 @@
       </c>
       <c r="C19" s="2" t="inlineStr">
         <is>
-          <t>5,2; 32,59</t>
+          <t>3,02; 31,24</t>
         </is>
       </c>
       <c r="D19" s="2" t="inlineStr">
         <is>
-          <t>-5,99; 19,49</t>
+          <t>-5,32; 21,54</t>
         </is>
       </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
-          <t>118,56; 162,16</t>
+          <t>119,54; 163,04</t>
         </is>
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>1,67; 25,45</t>
+          <t>-0,18; 24,89</t>
         </is>
       </c>
       <c r="G19" s="2" t="inlineStr">
         <is>
-          <t>-14,48; 7,59</t>
+          <t>-14,91; 7,42</t>
         </is>
       </c>
       <c r="H19" s="2" t="inlineStr">
         <is>
-          <t>103,22; 139,85</t>
+          <t>104,49; 141,65</t>
         </is>
       </c>
       <c r="I19" s="2" t="inlineStr">
         <is>
-          <t>5,71; 23,8</t>
+          <t>5,42; 24,75</t>
         </is>
       </c>
       <c r="J19" s="2" t="inlineStr">
         <is>
-          <t>-7,52; 9,45</t>
+          <t>-7,67; 9,79</t>
         </is>
       </c>
       <c r="K19" s="2" t="inlineStr">
         <is>
-          <t>116,94; 142,64</t>
+          <t>114,4; 143,65</t>
         </is>
       </c>
     </row>

--- a/data/trans_camb/P2A_enfcro_R-Estudios-trans_camb.xlsx
+++ b/data/trans_camb/P2A_enfcro_R-Estudios-trans_camb.xlsx
@@ -677,47 +677,47 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
-          <t>-10,12; 19,46</t>
+          <t>-12,06; 19,87</t>
         </is>
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>-17,65; 16,49</t>
+          <t>-16,95; 13,95</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>21,91; 46,31</t>
+          <t>21,22; 46,69</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>-15,77; 13,71</t>
+          <t>-16,99; 14,78</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
         <is>
-          <t>-29,93; 1,25</t>
+          <t>-30,13; 1,76</t>
         </is>
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>13,47; 38,28</t>
+          <t>13,48; 38,2</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>-10,6; 11,2</t>
+          <t>-8,14; 12,49</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
         <is>
-          <t>-20,07; 2,78</t>
+          <t>-19,3; 3,39</t>
         </is>
       </c>
       <c r="K5" s="2" t="inlineStr">
         <is>
-          <t>20,74; 38,45</t>
+          <t>20,2; 38,76</t>
         </is>
       </c>
     </row>
@@ -783,47 +783,47 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
-          <t>-15,76; 39,44</t>
+          <t>-19,18; 39,99</t>
         </is>
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>-27,82; 32,62</t>
+          <t>-26,91; 27,77</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>33,17; 98,59</t>
+          <t>31,25; 99,36</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>-22,41; 25,37</t>
+          <t>-24,28; 27,52</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
         <is>
-          <t>-42,74; 2,4</t>
+          <t>-43,77; 2,62</t>
         </is>
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>18,22; 71,87</t>
+          <t>19,01; 72,43</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>-16,08; 20,13</t>
+          <t>-12,61; 23,56</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
         <is>
-          <t>-31,01; 4,79</t>
+          <t>-29,85; 6,04</t>
         </is>
       </c>
       <c r="K7" s="2" t="inlineStr">
         <is>
-          <t>30,69; 72,12</t>
+          <t>30,59; 73,98</t>
         </is>
       </c>
     </row>
@@ -893,47 +893,47 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>0,22; 13,55</t>
+          <t>0,12; 13,34</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>-2,96; 9,09</t>
+          <t>-2,55; 9,87</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>50,54; 60,13</t>
+          <t>50,77; 60,65</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>0,2; 12,53</t>
+          <t>0,1; 12,14</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>-6,49; 4,94</t>
+          <t>-6,75; 5,32</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>46,68; 56,53</t>
+          <t>46,87; 56,74</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>2,19; 11,37</t>
+          <t>1,93; 10,96</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
         <is>
-          <t>-3,54; 4,93</t>
+          <t>-3,4; 5,16</t>
         </is>
       </c>
       <c r="K9" s="2" t="inlineStr">
         <is>
-          <t>50,19; 57,37</t>
+          <t>50,36; 57,05</t>
         </is>
       </c>
     </row>
@@ -999,47 +999,47 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
-          <t>0,63; 38,37</t>
+          <t>0,22; 37,66</t>
         </is>
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>-6,96; 25,08</t>
+          <t>-6,16; 29,06</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>118,21; 175,81</t>
+          <t>118,86; 176,34</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>0,42; 32,48</t>
+          <t>0,31; 31,5</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
         <is>
-          <t>-14,48; 12,78</t>
+          <t>-15,22; 13,52</t>
         </is>
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>99,65; 147,68</t>
+          <t>101,15; 149,65</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>4,87; 29,39</t>
+          <t>4,54; 28,67</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
         <is>
-          <t>-8,35; 12,63</t>
+          <t>-7,93; 13,39</t>
         </is>
       </c>
       <c r="K11" s="2" t="inlineStr">
         <is>
-          <t>115,32; 152,75</t>
+          <t>116,98; 152,82</t>
         </is>
       </c>
     </row>
@@ -1109,47 +1109,47 @@
       </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
-          <t>-3,51; 17,42</t>
+          <t>-3,63; 17,04</t>
         </is>
       </c>
       <c r="D13" s="2" t="inlineStr">
         <is>
-          <t>-4,05; 15,16</t>
+          <t>-4,92; 14,53</t>
         </is>
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>58,25; 71,56</t>
+          <t>57,14; 71,06</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>-5,43; 14,69</t>
+          <t>-4,92; 15,33</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
         <is>
-          <t>-8,36; 10,95</t>
+          <t>-8,08; 11,67</t>
         </is>
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>54,59; 68,93</t>
+          <t>54,61; 69,14</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>-1,13; 13,28</t>
+          <t>-1,1; 13,12</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
         <is>
-          <t>-2,71; 10,79</t>
+          <t>-3,24; 10,25</t>
         </is>
       </c>
       <c r="K13" s="2" t="inlineStr">
         <is>
-          <t>58,05; 68,4</t>
+          <t>58,87; 68,68</t>
         </is>
       </c>
     </row>
@@ -1215,47 +1215,47 @@
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
-          <t>-8,8; 56,8</t>
+          <t>-9,21; 55,88</t>
         </is>
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>-9,72; 50,0</t>
+          <t>-12,59; 48,08</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>140,29; 254,63</t>
+          <t>133,53; 247,0</t>
         </is>
       </c>
       <c r="F15" s="2" t="inlineStr">
         <is>
-          <t>-12,75; 46,24</t>
+          <t>-11,74; 49,29</t>
         </is>
       </c>
       <c r="G15" s="2" t="inlineStr">
         <is>
-          <t>-20,78; 34,54</t>
+          <t>-19,7; 37,0</t>
         </is>
       </c>
       <c r="H15" s="2" t="inlineStr">
         <is>
-          <t>124,04; 229,66</t>
+          <t>123,24; 230,69</t>
         </is>
       </c>
       <c r="I15" s="2" t="inlineStr">
         <is>
-          <t>-2,88; 41,35</t>
+          <t>-2,7; 40,57</t>
         </is>
       </c>
       <c r="J15" s="2" t="inlineStr">
         <is>
-          <t>-6,77; 33,69</t>
+          <t>-8,31; 32,02</t>
         </is>
       </c>
       <c r="K15" s="2" t="inlineStr">
         <is>
-          <t>142,16; 222,36</t>
+          <t>146,22; 224,06</t>
         </is>
       </c>
     </row>
@@ -1325,47 +1325,47 @@
       </c>
       <c r="C17" s="2" t="inlineStr">
         <is>
-          <t>1,3; 11,69</t>
+          <t>1,66; 11,84</t>
         </is>
       </c>
       <c r="D17" s="2" t="inlineStr">
         <is>
-          <t>-2,2; 7,93</t>
+          <t>-1,93; 7,82</t>
         </is>
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>51,47; 59,01</t>
+          <t>51,42; 59,12</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>-0,08; 9,98</t>
+          <t>0,74; 10,59</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
         <is>
-          <t>-6,51; 3,05</t>
+          <t>-6,86; 3,39</t>
         </is>
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>48,12; 55,69</t>
+          <t>48,09; 55,62</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>2,43; 9,85</t>
+          <t>2,51; 9,75</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
         <is>
-          <t>-3,34; 3,85</t>
+          <t>-3,24; 3,72</t>
         </is>
       </c>
       <c r="K17" s="2" t="inlineStr">
         <is>
-          <t>50,54; 56,17</t>
+          <t>50,92; 56,39</t>
         </is>
       </c>
     </row>
@@ -1431,47 +1431,47 @@
       </c>
       <c r="C19" s="2" t="inlineStr">
         <is>
-          <t>3,02; 31,24</t>
+          <t>4,02; 31,91</t>
         </is>
       </c>
       <c r="D19" s="2" t="inlineStr">
         <is>
-          <t>-5,32; 21,54</t>
+          <t>-4,77; 21,29</t>
         </is>
       </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
-          <t>119,54; 163,04</t>
+          <t>120,66; 162,59</t>
         </is>
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>-0,18; 24,89</t>
+          <t>1,49; 26,05</t>
         </is>
       </c>
       <c r="G19" s="2" t="inlineStr">
         <is>
-          <t>-14,91; 7,42</t>
+          <t>-15,01; 8,38</t>
         </is>
       </c>
       <c r="H19" s="2" t="inlineStr">
         <is>
-          <t>104,49; 141,65</t>
+          <t>103,95; 140,02</t>
         </is>
       </c>
       <c r="I19" s="2" t="inlineStr">
         <is>
-          <t>5,42; 24,75</t>
+          <t>5,73; 24,53</t>
         </is>
       </c>
       <c r="J19" s="2" t="inlineStr">
         <is>
-          <t>-7,67; 9,79</t>
+          <t>-7,53; 9,24</t>
         </is>
       </c>
       <c r="K19" s="2" t="inlineStr">
         <is>
-          <t>114,4; 143,65</t>
+          <t>117,49; 145,47</t>
         </is>
       </c>
     </row>

--- a/data/trans_camb/P2A_enfcro_R-Estudios-trans_camb.xlsx
+++ b/data/trans_camb/P2A_enfcro_R-Estudios-trans_camb.xlsx
@@ -529,14 +529,14 @@
       <c r="B1" s="2" t="n"/>
       <c r="C1" s="3" t="inlineStr">
         <is>
-          <t>Niña</t>
+          <t>Niño</t>
         </is>
       </c>
       <c r="D1" s="3" t="n"/>
       <c r="E1" s="3" t="n"/>
       <c r="F1" s="3" t="inlineStr">
         <is>
-          <t>Niño</t>
+          <t>Niña</t>
         </is>
       </c>
       <c r="G1" s="3" t="n"/>
@@ -624,32 +624,32 @@
       </c>
       <c r="C4" s="2" t="inlineStr">
         <is>
+          <t>-1,68</t>
+        </is>
+      </c>
+      <c r="D4" s="2" t="inlineStr">
+        <is>
+          <t>-14,22</t>
+        </is>
+      </c>
+      <c r="E4" s="2" t="inlineStr">
+        <is>
+          <t>25,32</t>
+        </is>
+      </c>
+      <c r="F4" s="2" t="inlineStr">
+        <is>
           <t>4,07</t>
         </is>
       </c>
-      <c r="D4" s="2" t="inlineStr">
+      <c r="G4" s="2" t="inlineStr">
         <is>
           <t>-1,64</t>
         </is>
       </c>
-      <c r="E4" s="2" t="inlineStr">
-        <is>
-          <t>33,52</t>
-        </is>
-      </c>
-      <c r="F4" s="2" t="inlineStr">
-        <is>
-          <t>-1,68</t>
-        </is>
-      </c>
-      <c r="G4" s="2" t="inlineStr">
-        <is>
-          <t>-14,22</t>
-        </is>
-      </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>25,47</t>
+          <t>32,24</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
@@ -664,7 +664,7 @@
       </c>
       <c r="K4" s="2" t="inlineStr">
         <is>
-          <t>29,56</t>
+          <t>28,86</t>
         </is>
       </c>
     </row>
@@ -677,47 +677,47 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
-          <t>-12,06; 19,87</t>
+          <t>-15,73; 13,9</t>
         </is>
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>-16,95; 13,95</t>
+          <t>-30,56; 1,74</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>21,22; 46,69</t>
+          <t>13,51; 39,48</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>-16,99; 14,78</t>
+          <t>-11,66; 18,62</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
         <is>
-          <t>-30,13; 1,76</t>
+          <t>-18,77; 14,58</t>
         </is>
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>13,48; 38,2</t>
+          <t>19,72; 45,2</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>-8,14; 12,49</t>
+          <t>-9,44; 12,04</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
         <is>
-          <t>-19,3; 3,39</t>
+          <t>-19,25; 2,3</t>
         </is>
       </c>
       <c r="K5" s="2" t="inlineStr">
         <is>
-          <t>20,2; 38,76</t>
+          <t>19,38; 37,6</t>
         </is>
       </c>
     </row>
@@ -730,32 +730,32 @@
       </c>
       <c r="C6" s="2" t="inlineStr">
         <is>
+          <t>-2,65%</t>
+        </is>
+      </c>
+      <c r="D6" s="2" t="inlineStr">
+        <is>
+          <t>-22,41%</t>
+        </is>
+      </c>
+      <c r="E6" s="2" t="inlineStr">
+        <is>
+          <t>39,89%</t>
+        </is>
+      </c>
+      <c r="F6" s="2" t="inlineStr">
+        <is>
           <t>7,06%</t>
         </is>
       </c>
-      <c r="D6" s="2" t="inlineStr">
+      <c r="G6" s="2" t="inlineStr">
         <is>
           <t>-2,85%</t>
         </is>
       </c>
-      <c r="E6" s="2" t="inlineStr">
-        <is>
-          <t>58,15%</t>
-        </is>
-      </c>
-      <c r="F6" s="2" t="inlineStr">
-        <is>
-          <t>-2,65%</t>
-        </is>
-      </c>
-      <c r="G6" s="2" t="inlineStr">
-        <is>
-          <t>-22,41%</t>
-        </is>
-      </c>
       <c r="H6" s="2" t="inlineStr">
         <is>
-          <t>40,14%</t>
+          <t>55,93%</t>
         </is>
       </c>
       <c r="I6" s="2" t="inlineStr">
@@ -770,7 +770,7 @@
       </c>
       <c r="K6" s="2" t="inlineStr">
         <is>
-          <t>48,93%</t>
+          <t>47,77%</t>
         </is>
       </c>
     </row>
@@ -783,47 +783,47 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
-          <t>-19,18; 39,99</t>
+          <t>-23,17; 25,21</t>
         </is>
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>-26,91; 27,77</t>
+          <t>-43,77; 3,38</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>31,25; 99,36</t>
+          <t>18,38; 74,94</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>-24,28; 27,52</t>
+          <t>-18,55; 37,43</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
         <is>
-          <t>-43,77; 2,62</t>
+          <t>-29,05; 29,59</t>
         </is>
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>19,01; 72,43</t>
+          <t>29,6; 94,82</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>-12,61; 23,56</t>
+          <t>-14,4; 21,96</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
         <is>
-          <t>-29,85; 6,04</t>
+          <t>-29,77; 4,09</t>
         </is>
       </c>
       <c r="K7" s="2" t="inlineStr">
         <is>
-          <t>30,59; 73,98</t>
+          <t>28,66; 71,13</t>
         </is>
       </c>
     </row>
@@ -840,32 +840,32 @@
       </c>
       <c r="C8" s="2" t="inlineStr">
         <is>
+          <t>6,2</t>
+        </is>
+      </c>
+      <c r="D8" s="2" t="inlineStr">
+        <is>
+          <t>-0,96</t>
+        </is>
+      </c>
+      <c r="E8" s="2" t="inlineStr">
+        <is>
+          <t>52,22</t>
+        </is>
+      </c>
+      <c r="F8" s="2" t="inlineStr">
+        <is>
           <t>7,12</t>
         </is>
       </c>
-      <c r="D8" s="2" t="inlineStr">
+      <c r="G8" s="2" t="inlineStr">
         <is>
           <t>3,07</t>
         </is>
       </c>
-      <c r="E8" s="2" t="inlineStr">
-        <is>
-          <t>55,42</t>
-        </is>
-      </c>
-      <c r="F8" s="2" t="inlineStr">
-        <is>
-          <t>6,2</t>
-        </is>
-      </c>
-      <c r="G8" s="2" t="inlineStr">
-        <is>
-          <t>-0,96</t>
-        </is>
-      </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>52,2</t>
+          <t>55,11</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
@@ -880,7 +880,7 @@
       </c>
       <c r="K8" s="2" t="inlineStr">
         <is>
-          <t>53,7</t>
+          <t>53,57</t>
         </is>
       </c>
     </row>
@@ -893,47 +893,47 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>0,12; 13,34</t>
+          <t>-0,51; 12,11</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>-2,55; 9,87</t>
+          <t>-6,46; 5,83</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>50,77; 60,65</t>
+          <t>47,82; 57,16</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>0,1; 12,14</t>
+          <t>-0,04; 13,27</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>-6,75; 5,32</t>
+          <t>-3,21; 8,93</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>46,87; 56,74</t>
+          <t>49,81; 59,83</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>1,93; 10,96</t>
+          <t>2,29; 10,94</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
         <is>
-          <t>-3,4; 5,16</t>
+          <t>-3,38; 5,15</t>
         </is>
       </c>
       <c r="K9" s="2" t="inlineStr">
         <is>
-          <t>50,36; 57,05</t>
+          <t>50,11; 56,77</t>
         </is>
       </c>
     </row>
@@ -946,32 +946,32 @@
       </c>
       <c r="C10" s="2" t="inlineStr">
         <is>
+          <t>14,8%</t>
+        </is>
+      </c>
+      <c r="D10" s="2" t="inlineStr">
+        <is>
+          <t>-2,28%</t>
+        </is>
+      </c>
+      <c r="E10" s="2" t="inlineStr">
+        <is>
+          <t>124,71%</t>
+        </is>
+      </c>
+      <c r="F10" s="2" t="inlineStr">
+        <is>
           <t>18,4%</t>
         </is>
       </c>
-      <c r="D10" s="2" t="inlineStr">
+      <c r="G10" s="2" t="inlineStr">
         <is>
           <t>7,93%</t>
         </is>
       </c>
-      <c r="E10" s="2" t="inlineStr">
-        <is>
-          <t>143,21%</t>
-        </is>
-      </c>
-      <c r="F10" s="2" t="inlineStr">
-        <is>
-          <t>14,8%</t>
-        </is>
-      </c>
-      <c r="G10" s="2" t="inlineStr">
-        <is>
-          <t>-2,28%</t>
-        </is>
-      </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>124,66%</t>
+          <t>142,41%</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
@@ -986,7 +986,7 @@
       </c>
       <c r="K10" s="2" t="inlineStr">
         <is>
-          <t>132,97%</t>
+          <t>132,63%</t>
         </is>
       </c>
     </row>
@@ -999,47 +999,47 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
-          <t>0,22; 37,66</t>
+          <t>-1,19; 30,24</t>
         </is>
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>-6,16; 29,06</t>
+          <t>-14,29; 15,38</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>118,86; 176,34</t>
+          <t>104,42; 151,45</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>0,31; 31,5</t>
+          <t>-0,14; 36,88</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
         <is>
-          <t>-15,22; 13,52</t>
+          <t>-7,6; 25,13</t>
         </is>
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>101,15; 149,65</t>
+          <t>114,8; 172,73</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>4,54; 28,67</t>
+          <t>5,41; 28,33</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
         <is>
-          <t>-7,93; 13,39</t>
+          <t>-7,97; 13,74</t>
         </is>
       </c>
       <c r="K11" s="2" t="inlineStr">
         <is>
-          <t>116,98; 152,82</t>
+          <t>115,78; 151,53</t>
         </is>
       </c>
     </row>
@@ -1056,32 +1056,32 @@
       </c>
       <c r="C12" s="2" t="inlineStr">
         <is>
+          <t>5,03</t>
+        </is>
+      </c>
+      <c r="D12" s="2" t="inlineStr">
+        <is>
+          <t>1,69</t>
+        </is>
+      </c>
+      <c r="E12" s="2" t="inlineStr">
+        <is>
+          <t>61,84</t>
+        </is>
+      </c>
+      <c r="F12" s="2" t="inlineStr">
+        <is>
           <t>6,78</t>
         </is>
       </c>
-      <c r="D12" s="2" t="inlineStr">
+      <c r="G12" s="2" t="inlineStr">
         <is>
           <t>5,11</t>
         </is>
       </c>
-      <c r="E12" s="2" t="inlineStr">
-        <is>
-          <t>64,84</t>
-        </is>
-      </c>
-      <c r="F12" s="2" t="inlineStr">
-        <is>
-          <t>5,03</t>
-        </is>
-      </c>
-      <c r="G12" s="2" t="inlineStr">
-        <is>
-          <t>1,69</t>
-        </is>
-      </c>
       <c r="H12" s="2" t="inlineStr">
         <is>
-          <t>61,86</t>
+          <t>64,76</t>
         </is>
       </c>
       <c r="I12" s="2" t="inlineStr">
@@ -1096,7 +1096,7 @@
       </c>
       <c r="K12" s="2" t="inlineStr">
         <is>
-          <t>63,36</t>
+          <t>63,32</t>
         </is>
       </c>
     </row>
@@ -1109,47 +1109,47 @@
       </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
-          <t>-3,63; 17,04</t>
+          <t>-3,89; 15,2</t>
         </is>
       </c>
       <c r="D13" s="2" t="inlineStr">
         <is>
-          <t>-4,92; 14,53</t>
+          <t>-8,15; 10,62</t>
         </is>
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>57,14; 71,06</t>
+          <t>54,84; 68,93</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>-4,92; 15,33</t>
+          <t>-2,27; 17,45</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
         <is>
-          <t>-8,08; 11,67</t>
+          <t>-4,37; 14,34</t>
         </is>
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>54,61; 69,14</t>
+          <t>58,08; 72,04</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>-1,1; 13,12</t>
+          <t>-1,04; 12,82</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
         <is>
-          <t>-3,24; 10,25</t>
+          <t>-3,47; 10,36</t>
         </is>
       </c>
       <c r="K13" s="2" t="inlineStr">
         <is>
-          <t>58,87; 68,68</t>
+          <t>58,13; 68,01</t>
         </is>
       </c>
     </row>
@@ -1162,32 +1162,32 @@
       </c>
       <c r="C14" s="2" t="inlineStr">
         <is>
+          <t>13,65%</t>
+        </is>
+      </c>
+      <c r="D14" s="2" t="inlineStr">
+        <is>
+          <t>4,58%</t>
+        </is>
+      </c>
+      <c r="E14" s="2" t="inlineStr">
+        <is>
+          <t>167,71%</t>
+        </is>
+      </c>
+      <c r="F14" s="2" t="inlineStr">
+        <is>
           <t>19,49%</t>
         </is>
       </c>
-      <c r="D14" s="2" t="inlineStr">
+      <c r="G14" s="2" t="inlineStr">
         <is>
           <t>14,68%</t>
         </is>
       </c>
-      <c r="E14" s="2" t="inlineStr">
-        <is>
-          <t>186,4%</t>
-        </is>
-      </c>
-      <c r="F14" s="2" t="inlineStr">
-        <is>
-          <t>13,65%</t>
-        </is>
-      </c>
-      <c r="G14" s="2" t="inlineStr">
-        <is>
-          <t>4,58%</t>
-        </is>
-      </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>167,77%</t>
+          <t>186,14%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
@@ -1202,7 +1202,7 @@
       </c>
       <c r="K14" s="2" t="inlineStr">
         <is>
-          <t>177,09%</t>
+          <t>177,0%</t>
         </is>
       </c>
     </row>
@@ -1215,47 +1215,47 @@
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
-          <t>-9,21; 55,88</t>
+          <t>-9,33; 48,06</t>
         </is>
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>-12,59; 48,08</t>
+          <t>-19,57; 33,48</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>133,53; 247,0</t>
+          <t>125,97; 229,34</t>
         </is>
       </c>
       <c r="F15" s="2" t="inlineStr">
         <is>
-          <t>-11,74; 49,29</t>
+          <t>-6,28; 57,1</t>
         </is>
       </c>
       <c r="G15" s="2" t="inlineStr">
         <is>
-          <t>-19,7; 37,0</t>
+          <t>-11,11; 47,89</t>
         </is>
       </c>
       <c r="H15" s="2" t="inlineStr">
         <is>
-          <t>123,24; 230,69</t>
+          <t>139,35; 256,72</t>
         </is>
       </c>
       <c r="I15" s="2" t="inlineStr">
         <is>
-          <t>-2,7; 40,57</t>
+          <t>-2,85; 39,49</t>
         </is>
       </c>
       <c r="J15" s="2" t="inlineStr">
         <is>
-          <t>-8,31; 32,02</t>
+          <t>-9,04; 31,68</t>
         </is>
       </c>
       <c r="K15" s="2" t="inlineStr">
         <is>
-          <t>146,22; 224,06</t>
+          <t>142,73; 218,41</t>
         </is>
       </c>
     </row>
@@ -1272,32 +1272,32 @@
       </c>
       <c r="C16" s="2" t="inlineStr">
         <is>
+          <t>5,28</t>
+        </is>
+      </c>
+      <c r="D16" s="2" t="inlineStr">
+        <is>
+          <t>-1,72</t>
+        </is>
+      </c>
+      <c r="E16" s="2" t="inlineStr">
+        <is>
+          <t>51,97</t>
+        </is>
+      </c>
+      <c r="F16" s="2" t="inlineStr">
+        <is>
           <t>6,86</t>
         </is>
       </c>
-      <c r="D16" s="2" t="inlineStr">
+      <c r="G16" s="2" t="inlineStr">
         <is>
           <t>2,62</t>
         </is>
       </c>
-      <c r="E16" s="2" t="inlineStr">
-        <is>
-          <t>55,35</t>
-        </is>
-      </c>
-      <c r="F16" s="2" t="inlineStr">
-        <is>
-          <t>5,28</t>
-        </is>
-      </c>
-      <c r="G16" s="2" t="inlineStr">
-        <is>
-          <t>-1,72</t>
-        </is>
-      </c>
       <c r="H16" s="2" t="inlineStr">
         <is>
-          <t>51,97</t>
+          <t>55,12</t>
         </is>
       </c>
       <c r="I16" s="2" t="inlineStr">
@@ -1312,7 +1312,7 @@
       </c>
       <c r="K16" s="2" t="inlineStr">
         <is>
-          <t>53,61</t>
+          <t>53,51</t>
         </is>
       </c>
     </row>
@@ -1325,47 +1325,47 @@
       </c>
       <c r="C17" s="2" t="inlineStr">
         <is>
-          <t>1,66; 11,84</t>
+          <t>0,78; 10,25</t>
         </is>
       </c>
       <c r="D17" s="2" t="inlineStr">
         <is>
-          <t>-1,93; 7,82</t>
+          <t>-6,55; 3,11</t>
         </is>
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>51,42; 59,12</t>
+          <t>48,03; 55,71</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>0,74; 10,59</t>
+          <t>2,14; 12,01</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
         <is>
-          <t>-6,86; 3,39</t>
+          <t>-2,49; 7,43</t>
         </is>
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>48,09; 55,62</t>
+          <t>51,07; 58,8</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>2,51; 9,75</t>
+          <t>2,46; 9,48</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
         <is>
-          <t>-3,24; 3,72</t>
+          <t>-3,25; 3,7</t>
         </is>
       </c>
       <c r="K17" s="2" t="inlineStr">
         <is>
-          <t>50,92; 56,39</t>
+          <t>50,83; 55,88</t>
         </is>
       </c>
     </row>
@@ -1378,32 +1378,32 @@
       </c>
       <c r="C18" s="2" t="inlineStr">
         <is>
+          <t>12,34%</t>
+        </is>
+      </c>
+      <c r="D18" s="2" t="inlineStr">
+        <is>
+          <t>-4,01%</t>
+        </is>
+      </c>
+      <c r="E18" s="2" t="inlineStr">
+        <is>
+          <t>121,42%</t>
+        </is>
+      </c>
+      <c r="F18" s="2" t="inlineStr">
+        <is>
           <t>17,27%</t>
         </is>
       </c>
-      <c r="D18" s="2" t="inlineStr">
+      <c r="G18" s="2" t="inlineStr">
         <is>
           <t>6,59%</t>
         </is>
       </c>
-      <c r="E18" s="2" t="inlineStr">
-        <is>
-          <t>139,21%</t>
-        </is>
-      </c>
-      <c r="F18" s="2" t="inlineStr">
-        <is>
-          <t>12,34%</t>
-        </is>
-      </c>
-      <c r="G18" s="2" t="inlineStr">
-        <is>
-          <t>-4,01%</t>
-        </is>
-      </c>
       <c r="H18" s="2" t="inlineStr">
         <is>
-          <t>121,43%</t>
+          <t>138,63%</t>
         </is>
       </c>
       <c r="I18" s="2" t="inlineStr">
@@ -1418,7 +1418,7 @@
       </c>
       <c r="K18" s="2" t="inlineStr">
         <is>
-          <t>129,75%</t>
+          <t>129,49%</t>
         </is>
       </c>
     </row>
@@ -1431,47 +1431,47 @@
       </c>
       <c r="C19" s="2" t="inlineStr">
         <is>
-          <t>4,02; 31,91</t>
+          <t>1,67; 25,45</t>
         </is>
       </c>
       <c r="D19" s="2" t="inlineStr">
         <is>
-          <t>-4,77; 21,29</t>
+          <t>-14,48; 7,59</t>
         </is>
       </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
-          <t>120,66; 162,59</t>
+          <t>103,51; 140,34</t>
         </is>
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>1,49; 26,05</t>
+          <t>5,2; 32,59</t>
         </is>
       </c>
       <c r="G19" s="2" t="inlineStr">
         <is>
-          <t>-15,01; 8,38</t>
+          <t>-5,99; 19,49</t>
         </is>
       </c>
       <c r="H19" s="2" t="inlineStr">
         <is>
-          <t>103,95; 140,02</t>
+          <t>117,69; 161,26</t>
         </is>
       </c>
       <c r="I19" s="2" t="inlineStr">
         <is>
-          <t>5,73; 24,53</t>
+          <t>5,71; 23,8</t>
         </is>
       </c>
       <c r="J19" s="2" t="inlineStr">
         <is>
-          <t>-7,53; 9,24</t>
+          <t>-7,52; 9,45</t>
         </is>
       </c>
       <c r="K19" s="2" t="inlineStr">
         <is>
-          <t>117,49; 145,47</t>
+          <t>116,67; 142,56</t>
         </is>
       </c>
     </row>
